--- a/outputs/evaluation/architecture/validation/CF_M04/run_3/CF_M04_arch_eval_llm_report.xlsx
+++ b/outputs/evaluation/architecture/validation/CF_M04/run_3/CF_M04_arch_eval_llm_report.xlsx
@@ -481,70 +481,66 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AU_14</t>
+          <t>AU_08</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>JSON</t>
+          <t>AI Service</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Data format used for requests and responses.</t>
+          <t>External service used for generating response suggestions for reviews.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>55, 69</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>AU_12, AU_21</t>
+          <t>AU_02</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>CF_M04_AU29</t>
+          <t>CF_M04_AU15</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Communication between the front-end and the back-end is done through a REST API, using JSON format messages for both requests and responses.</t>
+          <t>Finally, the system integrates several external services through the back-end, such as artificial intelligence services (Gemini or ChatGPT)</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0.7808</v>
+        <v>0.7329</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AU_15</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>AI Service</t>
-        </is>
-      </c>
+          <t>AU_17</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Service</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>External service for generating review responses.</t>
+          <t>La persistència de les dades es realitza mitjançant una base de dades relacional MySQL, gestionada a través de l’ORM de Django.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -554,35 +550,43 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>AU_08</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
+          <t>AU_05, AU_11</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>infrastructure layer, mysql</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>CF_M04_AU15</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
+          <t>CF_M04_P07</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>ORM</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Finally, the system integrates several external services through the back-end, such as artificial intelligence services (Gemini or ChatGPT)</t>
+          <t>The database uses MySQL as a relational engine. The tables and relationships are defined using Django's ORM, allowing for easy migration management and ensuring the coherence of the scheme.</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0.7329</v>
+        <v>0.7435</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AU_19</t>
+          <t>AU_20</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Google OAuth 2.0</t>
+          <t>JSON</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -592,90 +596,82 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Authentication provider used for user login.</t>
+          <t>Les dades s’intercanvien en format JSON, utilitzant mètodes HTTP estàndard com GET i POST.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>66</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>AU_18</t>
+          <t>AU_15</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>CF_M04_AU26</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Google Login</t>
-        </is>
-      </c>
+          <t>CF_M04_AU29</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Authentication services, such as Google login.</t>
+          <t>Communication between the front-end and the back-end is done through a REST API, using JSON format messages for both requests and responses.</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0.795</v>
+        <v>0.7808</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P_05</t>
+          <t>P_01</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Dependency Inversion (DIP)</t>
+          <t>Client-Server</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Design Pattern</t>
+          <t>Architectural Pattern</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>The domain defines interfaces that are implemented by the infrastructure.</t>
+          <t>The system follows a client-server architecture where the mobile application acts as the frontend and the server processes requests.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>P_01</t>
-        </is>
-      </c>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>CF_M04_P02</t>
+          <t>CF_M04_AU17</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Hierarchical model</t>
+          <t>HTTP</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>The app's navigation mainly follows a hierarchical model, in which the user accesses the main functionalities from a reduced set of base screens.</t>
+          <t>Communication is done through an HTTP-based REST API. Data is exchanged in JSON format, using standard HTTP methods such as GET and POST.</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0.6261</v>
+        <v>0.727</v>
       </c>
     </row>
   </sheetData>
